--- a/data/trans_dic/P33B_R5-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R5-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,76; 17,29</t>
+          <t>11,37; 16,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,39; 29,31</t>
+          <t>24,31; 29,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,93; 23,92</t>
+          <t>19,5; 23,22</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,84</t>
+          <t>4,51; 6,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,2</t>
+          <t>8,15; 10,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 7,17</t>
+          <t>6,5; 7,93</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,67</t>
+          <t>3,79; 7,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 9,33</t>
+          <t>6,23; 9,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 7,78</t>
+          <t>5,47; 7,82</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 7,29</t>
+          <t>5,85; 7,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 12,96</t>
+          <t>11,71; 13,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,76; 9,88</t>
+          <t>9,18; 10,45</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>74100</t>
+          <t>80212</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>200940</t>
+          <t>218810</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275040</t>
+          <t>299022</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>60461; 88868</t>
+          <t>65669; 95923</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>183556; 220597</t>
+          <t>199519; 239313</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>252431; 302921</t>
+          <t>272615; 324722</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>108930</t>
+          <t>119307</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>175800</t>
+          <t>197616</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>284730</t>
+          <t>316924</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74703; 133639</t>
+          <t>100616; 144613</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>129865; 205852</t>
+          <t>176965; 223155</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>228845; 324619</t>
+          <t>285931; 349004</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35886</t>
+          <t>38057</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49618</t>
+          <t>56466</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85504</t>
+          <t>94523</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25594; 49579</t>
+          <t>27002; 51946</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39211; 61612</t>
+          <t>45804; 69919</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70016; 101651</t>
+          <t>79194; 113052</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>218916</t>
+          <t>237576</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>426358</t>
+          <t>472893</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>645274</t>
+          <t>710469</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>169110; 251578</t>
+          <t>205966; 266049</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>353161; 473021</t>
+          <t>436495; 506223</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>551243; 701444</t>
+          <t>665372; 757387</t>
         </is>
       </c>
     </row>
